--- a/HaluProject/Halu/Application/Sample/ExcelTemplate/Apps/OrderListPrint/OrderListPrint_printH.xlsx
+++ b/HaluProject/Halu/Application/Sample/ExcelTemplate/Apps/OrderListPrint/OrderListPrint_printH.xlsx
@@ -1,137 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_tills\halu\HaluProject\Halu\Application\Sample\ExcelTemplate\Apps\OrderListPrint\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5784D527-F76D-4F3E-93E0-82918E3256C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86314138-6E98-425D-8579-65F28FDD26D8}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>受注番号</t>
-    <rPh sb="0" eb="2">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>バンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>受注日</t>
-    <rPh sb="0" eb="3">
-      <t>ジュチュウビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>受注金額</t>
-    <rPh sb="0" eb="2">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キンガク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>明細数</t>
-    <rPh sb="0" eb="2">
-      <t>メイサイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>顧客氏名</t>
-    <rPh sb="0" eb="2">
-      <t>コキャク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>顧客氏名</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>受注日FROM</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>受注日TO</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>受注一覧表（Ｈ）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ページ：</t>
-    <phoneticPr fontId="1"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="164" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="165" formatCode="0_ "/>
+    <numFmt numFmtId="166" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -228,73 +136,158 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -594,207 +587,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40EBDEC-E849-4111-855F-36B902BDF26B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="2" width="26.25" customWidth="1"/>
-    <col min="3" max="3" width="13.75" customWidth="1"/>
-    <col min="4" max="4" width="13.125" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col width="12.875" customWidth="1" style="16" min="1" max="1"/>
+    <col width="26.25" customWidth="1" style="16" min="2" max="2"/>
+    <col width="13.75" customWidth="1" style="16" min="3" max="3"/>
+    <col width="13.125" customWidth="1" style="16" min="4" max="4"/>
+    <col width="12.75" customWidth="1" style="16" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B1" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="B5" s="6"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="12"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="9"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="9"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="10"/>
+    <row r="1">
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>受注一覧表（Ｈ）</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>ページ：</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>顧客氏名</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>受注日FROM</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>受注日TO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="19" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>受注番号</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>顧客氏名</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>受注日</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>受注金額</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>明細数</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="23" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="23" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="23" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="23" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="23" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="23" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="23" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="23" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="23" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="23" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="23" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="23" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="23" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="23" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>